--- a/tests/fixtures/dimensions/calibri.xlsx
+++ b/tests/fixtures/dimensions/calibri.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GitHub\pyOpenVBA\tests\fixtures\dimensions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{600A2E75-219D-49DB-9231-E6927E815971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D90BFF9-6EC0-480F-946E-AB1AF68AE510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="19440" windowHeight="11220" xr2:uid="{240A3E50-B9D6-47E0-8C96-2BCEB10FCCBF}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="19440" windowHeight="11220" xr2:uid="{39FDA70F-29D5-4460-97AE-DA5B61C6C575}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -403,7 +403,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27C1C27E-90A4-4C0B-A2EF-32E351C7764E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5503EE1-784F-4176-80BC-FBCDBBA04B37}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/tests/fixtures/dimensions/calibri.xlsx
+++ b/tests/fixtures/dimensions/calibri.xlsx
@@ -3,11 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GitHub\pyOpenVBA\tests\fixtures\dimensions\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{1D90BFF9-6EC0-480F-946E-AB1AF68AE510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1950" yWindow="1950" windowWidth="19440" windowHeight="11220" xr2:uid="{39FDA70F-29D5-4460-97AE-DA5B61C6C575}"/>
